--- a/hira_material_automation/output/monthly/202601_202604__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__arthroscopy_cannula__041001__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:37:39</t>
+          <t>2026-04-14T21:55:39</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1bd1203830ff18b947a168cd979d53db1101e25a090f80bed69da4d6acf90177</t>
+          <t>0eb0ac1394c4f5c73ae5dea4012f2629ece2b16fe50f5f3c2527c32cf716a582</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__arthroscopy_cannula__041001__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__arthroscopy_cannula__041001__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:55:39</t>
+          <t>2026-04-24T21:53:36</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0eb0ac1394c4f5c73ae5dea4012f2629ece2b16fe50f5f3c2527c32cf716a582</t>
+          <t>9d8e45fddfedc27ba853e1c3e42bdef555d8f429d29b9f433d7085912ff91d4e</t>
         </is>
       </c>
     </row>
